--- a/谱图/报告解析/ICP/称量记录0730.xlsx
+++ b/谱图/报告解析/ICP/称量记录0730.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0A1F86-33D3-40F5-9199-2C6FA7434B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB69D7D0-57C0-4FA3-968C-14BB539C771A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="16200" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>称样时间</t>
   </si>
@@ -31,15 +31,10 @@
     <t>试样描述</t>
   </si>
   <si>
-    <t>TN26070620001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>TN26070643</t>
   </si>
   <si>
-    <t>TN26070621001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TN26070622001</t>
+    <t>下下寻</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -393,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.46484375" customWidth="1"/>
@@ -423,24 +418,18 @@
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>46233</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>46233</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -513,7 +502,7 @@
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -523,7 +512,7 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -652,16 +641,6 @@
       <c r="A46" s="1"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="1"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="1"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/谱图/报告解析/ICP/称量记录0730.xlsx
+++ b/谱图/报告解析/ICP/称量记录0730.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB69D7D0-57C0-4FA3-968C-14BB539C771A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4F660D-A7AF-48F7-89D3-B513552F3F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,11 +31,11 @@
     <t>试样描述</t>
   </si>
   <si>
-    <t>TN26070643</t>
+    <t>下下寻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>下下寻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>TN26070830</t>
   </si>
 </sst>
 </file>
@@ -413,13 +413,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">

--- a/谱图/报告解析/ICP/称量记录0730.xlsx
+++ b/谱图/报告解析/ICP/称量记录0730.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4F660D-A7AF-48F7-89D3-B513552F3F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29355425-D7D7-4688-A3BB-A08A8E7A25F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,11 +31,11 @@
     <t>试样描述</t>
   </si>
   <si>
-    <t>下下寻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>TS26080751001</t>
   </si>
   <si>
-    <t>TN26070830</t>
+    <t>颗粒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -413,13 +413,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
